--- a/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0003T0006Z000C1N28_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0003T0006Z000C1N28_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>56.87565001348722</v>
+        <v>9.242293127191672</v>
       </c>
       <c r="D2" t="n">
-        <v>56.40456321687345</v>
+        <v>9.165741522741936</v>
       </c>
       <c r="E2" t="n">
-        <v>16.58959003759103</v>
+        <v>2.695808381108542</v>
       </c>
       <c r="F2" t="n">
-        <v>16.52283920130176</v>
+        <v>2.684961370211536</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>82.18841412917985</v>
+        <v>13.35561729599173</v>
       </c>
       <c r="D3" t="n">
-        <v>81.2248920658696</v>
+        <v>13.19904496070381</v>
       </c>
       <c r="E3" t="n">
-        <v>16.58959003759103</v>
+        <v>2.695808381108542</v>
       </c>
       <c r="F3" t="n">
-        <v>16.52283920130176</v>
+        <v>2.684961370211536</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>53.55882363001902</v>
+        <v>8.70330883987809</v>
       </c>
       <c r="D4" t="n">
-        <v>52.73227198851641</v>
+        <v>8.568994198133916</v>
       </c>
       <c r="E4" t="n">
-        <v>16.58959003759103</v>
+        <v>2.695808381108542</v>
       </c>
       <c r="F4" t="n">
-        <v>16.52283920130176</v>
+        <v>2.684961370211536</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>74.32215758864569</v>
+        <v>12.07735060815493</v>
       </c>
       <c r="D5" t="n">
-        <v>73.35825735382312</v>
+        <v>11.92071681999626</v>
       </c>
       <c r="E5" t="n">
-        <v>16.58959003759103</v>
+        <v>2.695808381108542</v>
       </c>
       <c r="F5" t="n">
-        <v>16.52283920130176</v>
+        <v>2.684961370211536</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>56.3335438677481</v>
+        <v>9.154200878509066</v>
       </c>
       <c r="D6" t="n">
-        <v>55.38641078309858</v>
+        <v>9.000291752253519</v>
       </c>
       <c r="E6" t="n">
-        <v>16.58959003759103</v>
+        <v>2.695808381108542</v>
       </c>
       <c r="F6" t="n">
-        <v>16.52283920130176</v>
+        <v>2.684961370211536</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>57.19796046320679</v>
+        <v>9.294668575271103</v>
       </c>
       <c r="D7" t="n">
-        <v>57.22422886689149</v>
+        <v>9.298937190869868</v>
       </c>
       <c r="E7" t="n">
-        <v>16.58959003759103</v>
+        <v>2.695808381108542</v>
       </c>
       <c r="F7" t="n">
-        <v>16.52283920130176</v>
+        <v>2.684961370211536</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>46.0956543724113</v>
+        <v>7.490543835516836</v>
       </c>
       <c r="D8" t="n">
-        <v>46.37082469788418</v>
+        <v>7.53525901340618</v>
       </c>
       <c r="E8" t="n">
-        <v>16.58959003759103</v>
+        <v>2.695808381108542</v>
       </c>
       <c r="F8" t="n">
-        <v>16.52283920130176</v>
+        <v>2.684961370211536</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>28.49983035046927</v>
+        <v>4.631222431951256</v>
       </c>
       <c r="D9" t="n">
-        <v>28.78021936708936</v>
+        <v>4.676785647152021</v>
       </c>
       <c r="E9" t="n">
-        <v>16.58959003759103</v>
+        <v>2.695808381108542</v>
       </c>
       <c r="F9" t="n">
-        <v>16.52283920130176</v>
+        <v>2.684961370211536</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>36.60833287534725</v>
+        <v>5.948854092243929</v>
       </c>
       <c r="D10" t="n">
-        <v>35.71136546937508</v>
+        <v>5.803096888773451</v>
       </c>
       <c r="E10" t="n">
-        <v>16.58959003759103</v>
+        <v>2.695808381108542</v>
       </c>
       <c r="F10" t="n">
-        <v>16.52283920130176</v>
+        <v>2.684961370211536</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>43.01145683494171</v>
+        <v>6.989361735678028</v>
       </c>
       <c r="D11" t="n">
-        <v>42.25349210544407</v>
+        <v>6.866192467134661</v>
       </c>
       <c r="E11" t="n">
-        <v>16.58959003759103</v>
+        <v>2.695808381108542</v>
       </c>
       <c r="F11" t="n">
-        <v>16.52283920130176</v>
+        <v>2.684961370211536</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>31.08840688220807</v>
+        <v>5.051866118358812</v>
       </c>
       <c r="D12" t="n">
-        <v>31.98947984054412</v>
+        <v>5.19829047408842</v>
       </c>
       <c r="E12" t="n">
-        <v>16.58959003759103</v>
+        <v>2.695808381108542</v>
       </c>
       <c r="F12" t="n">
-        <v>16.52283920130176</v>
+        <v>2.684961370211536</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>68.85739491022241</v>
+        <v>11.18932667291114</v>
       </c>
       <c r="D13" t="n">
-        <v>69.66286101451647</v>
+        <v>11.32021491485893</v>
       </c>
       <c r="E13" t="n">
-        <v>16.58959003759103</v>
+        <v>2.695808381108542</v>
       </c>
       <c r="F13" t="n">
-        <v>16.52283920130176</v>
+        <v>2.684961370211536</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>35.35879006470859</v>
+        <v>5.745803385515146</v>
       </c>
       <c r="D14" t="n">
-        <v>35.17852502191155</v>
+        <v>5.716510316060628</v>
       </c>
       <c r="E14" t="n">
-        <v>16.58959003759103</v>
+        <v>2.695808381108542</v>
       </c>
       <c r="F14" t="n">
-        <v>16.52283920130176</v>
+        <v>2.684961370211536</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>49.76167858302139</v>
+        <v>8.086272769740976</v>
       </c>
       <c r="D15" t="n">
-        <v>49.60828455065047</v>
+        <v>8.061346239480701</v>
       </c>
       <c r="E15" t="n">
-        <v>16.58959003759103</v>
+        <v>2.695808381108542</v>
       </c>
       <c r="F15" t="n">
-        <v>16.52283920130176</v>
+        <v>2.684961370211536</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>45.51735656826776</v>
+        <v>7.396570442343512</v>
       </c>
       <c r="D16" t="n">
-        <v>46.41045270305647</v>
+        <v>7.541698564246677</v>
       </c>
       <c r="E16" t="n">
-        <v>16.58959003759103</v>
+        <v>2.695808381108542</v>
       </c>
       <c r="F16" t="n">
-        <v>16.52283920130176</v>
+        <v>2.684961370211536</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>83.44911521162234</v>
+        <v>13.56048122188863</v>
       </c>
       <c r="D17" t="n">
-        <v>84.38978518513598</v>
+        <v>13.7133400925846</v>
       </c>
       <c r="E17" t="n">
-        <v>16.58959003759103</v>
+        <v>2.695808381108542</v>
       </c>
       <c r="F17" t="n">
-        <v>16.52283920130176</v>
+        <v>2.684961370211536</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
